--- a/vendor-portal/public/templates/vendor-payment-ledger.xlsx
+++ b/vendor-portal/public/templates/vendor-payment-ledger.xlsx
@@ -951,9 +951,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B843C46F-445E-4F12-990E-B5BFCC435A9A}">
-  <dimension ref="A1:AK19"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{B843C46F-445E-4F12-990E-B5BFCC435A9A}">
+  <dimension ref="A1:AN19"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" ns3:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
@@ -985,14 +985,17 @@
     <col min="30" max="30" width="13.1796875" customWidth="1"/>
     <col min="31" max="31" width="7.90625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.5" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" width="9.5" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" width="9.5" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" width="8" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" ht="21" ns3:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1049,17 +1052,24 @@
       </c>
       <c r="AE1" s="66"/>
       <c r="AF1" s="67"/>
-      <c r="AG1" s="11" t="s">
+      <c r="AG1" s="65" t="inlineStr">
+        <is>
+          <t>Payment Gateway Fee @2%</t>
+        </is>
+      </c>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="67"/>
+      <c r="AJ1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" s="51" t="s">
+      <c r="AK1" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
     </row>
-    <row r="2" spans="1:37" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" ht="87" customHeight="1" ns3:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1128,23 +1138,30 @@
       </c>
       <c r="AE2" s="45"/>
       <c r="AF2" s="46"/>
-      <c r="AG2" s="12" t="s">
+      <c r="AG2" s="44" t="inlineStr">
+        <is>
+          <t>Payment Gateway Fee @2%</t>
+        </is>
+      </c>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="14" t="s">
+      <c r="AK2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AI2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AL2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AK2" s="14" t="s">
+      <c r="AN2" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" ns3:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1221,13 +1238,28 @@
       <c r="AF3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AG3" s="12"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="15"/>
-      <c r="AJ3" s="14"/>
+      <c r="AG3" s="12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="AH3" s="12" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="AI3" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="AJ3" s="12"/>
       <c r="AK3" s="14"/>
+      <c r="AL3" s="15"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" ns3:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1349,17 +1381,26 @@
       <c r="AG4" s="13">
         <v>0</v>
       </c>
-      <c r="AH4" s="16"/>
-      <c r="AI4" s="17"/>
-      <c r="AJ4" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="19">
-        <f>Z4-AC4-AF4+AG4</f>
+      <c r="AH4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="16"/>
+      <c r="AL4" s="17"/>
+      <c r="AM4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="19">
+        <f>Z4-AC4-AF4-AI4+AJ4</f>
         <v>1124.2955079999999</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" ns3:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -1481,17 +1522,26 @@
       <c r="AG5" s="13">
         <v>0</v>
       </c>
-      <c r="AH5" s="16"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="19">
+      <c r="AH5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="16"/>
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="19">
         <f>AK4+Z5</f>
         <v>3589.0256360000003</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" ns3:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>38</v>
       </c>
@@ -1613,17 +1663,26 @@
       <c r="AG6" s="13">
         <v>0</v>
       </c>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="19">
+      <c r="AH6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="19">
         <f t="shared" ref="AK6:AK13" si="22">AK5+Z6</f>
         <v>5571.3099400000001</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" ns3:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>39</v>
       </c>
@@ -1745,17 +1804,26 @@
       <c r="AG7" s="13">
         <v>0</v>
       </c>
-      <c r="AH7" s="16"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="19">
+      <c r="AH7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="16"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="19">
         <f t="shared" si="22"/>
         <v>7963.8519479999995</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" ns3:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
@@ -1877,17 +1945,26 @@
       <c r="AG8" s="13">
         <v>0</v>
       </c>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="19">
+      <c r="AH8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="19">
         <f t="shared" si="22"/>
         <v>5499.1218199999994</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" ns3:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
@@ -2009,18 +2086,27 @@
       <c r="AG9" s="13">
         <v>0</v>
       </c>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="18">
+      <c r="AH9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="18">
         <f>-Z4</f>
         <v>-1124.2955079999999</v>
       </c>
-      <c r="AK9" s="19">
+      <c r="AN9" s="19">
         <f>AK8+AJ9</f>
         <v>4374.8263119999992</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" ns3:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
@@ -2142,17 +2228,26 @@
       <c r="AG10" s="13">
         <v>0</v>
       </c>
-      <c r="AH10" s="16"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="19">
+      <c r="AH10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="19">
         <f t="shared" si="22"/>
         <v>6576.6578399999989</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" ns3:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>44</v>
       </c>
@@ -2274,17 +2369,26 @@
       <c r="AG11" s="13">
         <v>0</v>
       </c>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="19">
+      <c r="AH11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="19">
         <f t="shared" si="22"/>
         <v>8688.494867999998</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" ns3:dyDescent="0.35">
       <c r="A12" s="28" t="s">
         <v>38</v>
       </c>
@@ -2403,20 +2507,29 @@
         <f t="shared" si="21"/>
         <v>23.6</v>
       </c>
-      <c r="AG12" s="33">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="35"/>
-      <c r="AJ12" s="36">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="37">
+      <c r="AG12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="33">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="34"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="36">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="37">
         <f t="shared" si="22"/>
         <v>6706.2105639999982</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" ht="15.5" ns3:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
@@ -2535,19 +2648,28 @@
         <v>0</v>
       </c>
       <c r="AG13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="13">
         <v>180</v>
       </c>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="19">
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="19">
         <f t="shared" si="22"/>
         <v>6886.2105639999982</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" ns3:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
@@ -2668,17 +2790,26 @@
       <c r="AG14" s="13">
         <v>0</v>
       </c>
-      <c r="AH14" s="16"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="19">
+      <c r="AH14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="16"/>
+      <c r="AL14" s="17"/>
+      <c r="AM14" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="19">
         <f t="shared" ref="AK14" si="35">AK13+Z14</f>
         <v>4774.3735359999982</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" ns3:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
@@ -2800,17 +2931,26 @@
       <c r="AG15" s="13">
         <v>0</v>
       </c>
-      <c r="AH15" s="16"/>
-      <c r="AI15" s="17"/>
-      <c r="AJ15" s="19">
+      <c r="AH15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="16"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="19">
         <v>-2201.8315280000002</v>
       </c>
-      <c r="AK15" s="19">
+      <c r="AN15" s="19">
         <f>AK14+AJ15</f>
         <v>2572.5420079999981</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" ns3:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>9</v>
       </c>
@@ -2932,17 +3072,26 @@
       <c r="AG16" s="13">
         <v>0</v>
       </c>
-      <c r="AH16" s="16"/>
-      <c r="AI16" s="17"/>
-      <c r="AJ16" s="19">
+      <c r="AH16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="16"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="19">
         <v>-180</v>
       </c>
-      <c r="AK16" s="19">
+      <c r="AN16" s="19">
         <f>AK15+AJ16</f>
         <v>2392.5420079999981</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" ns3:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>57</v>
       </c>
@@ -3064,17 +3213,26 @@
       <c r="AG17" s="13">
         <v>0</v>
       </c>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="17"/>
-      <c r="AJ17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="19">
+      <c r="AH17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="19">
         <f>AK16+Z17</f>
         <v>5146.4011359999986</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:37" ns3:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
@@ -3196,17 +3354,26 @@
       <c r="AG18" s="13">
         <v>0</v>
       </c>
-      <c r="AH18" s="16"/>
-      <c r="AI18" s="17"/>
-      <c r="AJ18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="19">
+      <c r="AH18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="16"/>
+      <c r="AL18" s="17"/>
+      <c r="AM18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="19">
         <f>AK17+Z18</f>
         <v>3034.5641079999987</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:37" ns3:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>59</v>
       </c>
@@ -3326,19 +3493,28 @@
       <c r="AG19" s="13">
         <v>0</v>
       </c>
-      <c r="AH19" s="16"/>
-      <c r="AI19" s="17"/>
-      <c r="AJ19" s="19">
+      <c r="AH19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="16"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="19">
         <v>-2201.83</v>
       </c>
-      <c r="AK19" s="19">
+      <c r="AN19" s="19">
         <f>AK18+AJ19</f>
         <v>832.73410799999874</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="AH1:AK1"/>
+  <mergeCells count="19">
+    <mergeCell ref="AK1:AN1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
@@ -3355,9 +3531,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AG2:AI2"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3" xr:uid="{39DB9B4E-F2E0-4CD1-8A08-E932A07AD756}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3" ns2:uid="{39DB9B4E-F2E0-4CD1-8A08-E932A07AD756}">
       <formula1>"Sale, Return, Claim, Payment, Cancellation"</formula1>
     </dataValidation>
   </dataValidations>
